--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12840,10 +12840,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M116" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N116" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.2</v>
+        <v>2.03</v>
       </c>
       <c r="M46" t="n">
         <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.03</v>
+        <v>4.2</v>
       </c>
       <c r="M47" t="n">
         <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>3.45</v>
+        <v>1.84</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13485,10 +13485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.03</v>
+        <v>4.2</v>
       </c>
       <c r="M46" t="n">
         <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>3.45</v>
+        <v>1.84</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.2</v>
+        <v>2.03</v>
       </c>
       <c r="M47" t="n">
         <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13098,10 +13098,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13485,10 +13485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="M110" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N110" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13098,10 +13098,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13872,10 +13872,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK133"/>
+  <dimension ref="A1:AK138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45933.39583333334</v>
+        <v>45933.375</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45933.41666666666</v>
+        <v>45933.39583333334</v>
       </c>
     </row>
     <row r="14">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45933.4375</v>
+        <v>45933.41666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45933.44791666666</v>
+        <v>45933.4375</v>
       </c>
     </row>
     <row r="18">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45933.45833333334</v>
+        <v>45933.44791666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45933.45833333334</v>
+        <v>45933.44791666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45933.46875</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45933.47916666666</v>
+        <v>45933.46875</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.47916666666</v>
       </c>
     </row>
     <row r="24">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45933.52083333334</v>
+        <v>45933.5</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45933.54166666666</v>
+        <v>45933.52083333334</v>
       </c>
     </row>
     <row r="38">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45933.5625</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45933.5625</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45933.57291666666</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.5625</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.5625</v>
       </c>
     </row>
     <row r="52">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.57291666666</v>
       </c>
     </row>
     <row r="53">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,27 +8626,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="65">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="M73" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N73" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9870,7 +9870,7 @@
         <v>2.2</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="78">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45933.63541666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45933.63541666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="96">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="97">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.63541666666</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.63541666666</v>
       </c>
     </row>
     <row r="100">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13614,10 +13614,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13872,10 +13872,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13915,27 +13915,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="106">
@@ -14044,27 +14044,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="107">
@@ -14173,27 +14173,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="108">
@@ -14302,12 +14302,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="109">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="M122" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N122" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="123">
@@ -16237,27 +16237,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="124">
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45933.67708333334</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="126">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45933.67708333334</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="127">
@@ -16753,27 +16753,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="AK127" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="128">
@@ -16882,27 +16882,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="129">
@@ -17011,27 +17011,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.67708333334</v>
       </c>
     </row>
     <row r="130">
@@ -17140,27 +17140,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45933.8125</v>
+        <v>45933.67708333334</v>
       </c>
     </row>
     <row r="131">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45933.875</v>
+        <v>45933.79166666666</v>
       </c>
     </row>
     <row r="132">
@@ -17398,12 +17398,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17518,7 +17518,7 @@
         <v>0</v>
       </c>
       <c r="AK132" s="3" t="n">
-        <v>45933.89583333334</v>
+        <v>45933.79166666666</v>
       </c>
     </row>
     <row r="133">
@@ -17527,126 +17527,771 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" s="3" t="n">
+        <v>45933.79166666666</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK134" s="3" t="n">
+        <v>45933.79166666666</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N135" t="n">
+        <v>3</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK135" s="3" t="n">
+        <v>45933.8125</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Houston Dash</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Orlando Pride</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" s="3" t="n">
+        <v>45933.875</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK137" s="3" t="n">
+        <v>45933.89583333334</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="inlineStr">
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK133" s="3" t="n">
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK138" s="3" t="n">
         <v>45933.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK138"/>
+  <dimension ref="A1:AK135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45933.375</v>
+        <v>45933.39583333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45933.39583333334</v>
+        <v>45933.41666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45933.41666666666</v>
+        <v>45933.4375</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45933.4375</v>
+        <v>45933.44791666666</v>
       </c>
     </row>
     <row r="18">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45933.44791666666</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="21">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45933.46875</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45933.47916666666</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.46875</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.47916666666</v>
       </c>
     </row>
     <row r="31">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.52083333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45933.52083333334</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5487,10 +5487,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45933.54166666666</v>
+        <v>45933.5625</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45933.54166666666</v>
+        <v>45933.5625</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45933.54166666666</v>
+        <v>45933.57291666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45933.54166666666</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45933.54166666666</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="50">
@@ -6820,27 +6820,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45933.5625</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45933.5625</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45933.57291666666</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="53">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="M61" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="64">
@@ -8626,27 +8626,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="65">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="M66" t="n">
         <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N67" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M68" t="n">
         <v>3.25</v>
       </c>
-      <c r="M68" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N68" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="M69" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N69" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="M71" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="N71" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N77" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="78">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="M81" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N81" t="n">
-        <v>2.4</v>
+        <v>3.95</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.63541666666</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.63541666666</v>
       </c>
     </row>
     <row r="96">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="97">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45933.63541666666</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13227,10 +13227,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45933.63541666666</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="100">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,55 +13569,55 @@
         </is>
       </c>
       <c r="L102" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M102" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N102" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z102" t="n">
         <v>2</v>
       </c>
-      <c r="M102" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N102" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>0</v>
-      </c>
       <c r="AA102" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="106">
@@ -14044,27 +14044,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="107">
@@ -14173,27 +14173,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="108">
@@ -14302,27 +14302,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14388,10 +14388,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="109">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.55</v>
+        <v>1.52</v>
       </c>
       <c r="M111" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N111" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15850,27 +15850,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16023,10 +16023,10 @@
         <v>2.05</v>
       </c>
       <c r="M121" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N121" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="Z121" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="123">
@@ -16237,27 +16237,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="124">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.67708333334</v>
       </c>
     </row>
     <row r="126">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.67708333334</v>
       </c>
     </row>
     <row r="127">
@@ -16753,12 +16753,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="AK127" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.75</v>
       </c>
     </row>
     <row r="128">
@@ -16882,27 +16882,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.79166666666</v>
       </c>
     </row>
     <row r="129">
@@ -17011,27 +17011,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45933.67708333334</v>
+        <v>45933.79166666666</v>
       </c>
     </row>
     <row r="130">
@@ -17140,27 +17140,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45933.67708333334</v>
+        <v>45933.79166666666</v>
       </c>
     </row>
     <row r="131">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17398,12 +17398,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17518,7 +17518,7 @@
         <v>0</v>
       </c>
       <c r="AK132" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.8125</v>
       </c>
     </row>
     <row r="133">
@@ -17527,12 +17527,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17647,7 +17647,7 @@
         <v>0</v>
       </c>
       <c r="AK133" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.875</v>
       </c>
     </row>
     <row r="134">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="AK134" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.89583333334</v>
       </c>
     </row>
     <row r="135">
@@ -17785,12 +17785,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17905,393 +17905,6 @@
         <v>0</v>
       </c>
       <c r="AK135" s="3" t="n">
-        <v>45933.8125</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>45933</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" t="n">
-        <v>0</v>
-      </c>
-      <c r="W136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK136" s="3" t="n">
-        <v>45933.875</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>45933</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK137" s="3" t="n">
-        <v>45933.89583333334</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>45933</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK138" s="3" t="n">
         <v>45933.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.29</v>
+        <v>2.4</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="M61" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N61" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="M64" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8709,7 +8709,7 @@
         <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="M66" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="M69" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9354,7 +9354,7 @@
         <v>2.2</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M77" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="M81" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N81" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.28</v>
+        <v>1.72</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N87" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="M92" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N92" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13227,10 +13227,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="M102" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N102" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="M105" t="n">
         <v>3.85</v>
       </c>
       <c r="N105" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="M106" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N106" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>8.5</v>
+        <v>2.45</v>
       </c>
       <c r="M108" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="N108" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,16 +14382,16 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="M109" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N109" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14646,10 +14646,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="M114" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N114" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Z114" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4455,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.41</v>
+        <v>3.04</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N34" t="n">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="M39" t="n">
-        <v>3.75</v>
+        <v>3.21</v>
       </c>
       <c r="N39" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.03</v>
+        <v>4.2</v>
       </c>
       <c r="M45" t="n">
         <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>3.45</v>
+        <v>1.84</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.2</v>
+        <v>2.03</v>
       </c>
       <c r="M46" t="n">
         <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N60" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N62" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="M63" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N63" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
       <c r="M66" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="M72" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N72" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N80" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="M81" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N81" t="n">
-        <v>4.05</v>
+        <v>2.18</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.72</v>
+        <v>2.87</v>
       </c>
       <c r="M87" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="N87" t="n">
-        <v>3.95</v>
+        <v>2.21</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,55 +12924,55 @@
         </is>
       </c>
       <c r="L97" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N97" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z97" t="n">
         <v>2</v>
       </c>
-      <c r="M97" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N97" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" t="n">
-        <v>0</v>
-      </c>
-      <c r="V97" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" t="n">
-        <v>0</v>
-      </c>
-      <c r="X97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>0</v>
-      </c>
       <c r="AA97" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13485,10 +13485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="M104" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N104" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="M108" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N108" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="M109" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N109" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="Z109" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>8.5</v>
+        <v>3.25</v>
       </c>
       <c r="M110" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,16 +14640,16 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.72</v>
+        <v>2.55</v>
       </c>
       <c r="M114" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N114" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z114" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15291,10 +15291,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.25</v>
+        <v>1.89</v>
       </c>
       <c r="M118" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="N118" t="n">
-        <v>2.1</v>
+        <v>3.73</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15675,7 +15675,7 @@
         <v>1.8</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,22 +16242,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="M132" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="N132" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4455,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="M60" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N60" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="M62" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="M63" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N64" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="N65" t="n">
         <v>2.3</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8921,17 +8921,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.85</v>
+        <v>3.79</v>
       </c>
       <c r="M67" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N67" t="n">
-        <v>2.6</v>
+        <v>1.84</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.54</v>
+        <v>3.25</v>
       </c>
       <c r="M71" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N74" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="M76" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="N76" t="n">
-        <v>2.61</v>
+        <v>3.95</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.06</v>
+        <v>2.87</v>
       </c>
       <c r="M85" t="n">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="N85" t="n">
-        <v>3.25</v>
+        <v>2.21</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="M86" t="n">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="N86" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="M97" t="n">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="N97" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13485,10 +13485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="M108" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N108" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.55</v>
+        <v>8.5</v>
       </c>
       <c r="M114" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="N114" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,16 +15156,16 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>8.5</v>
+        <v>2.55</v>
       </c>
       <c r="M115" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="N115" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,16 +15285,16 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA115" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="M116" t="n">
         <v>3.85</v>
       </c>
       <c r="N116" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="M118" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="N118" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15675,7 +15675,7 @@
         <v>1.8</v>
       </c>
       <c r="Z118" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="M119" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N119" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="M60" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="M62" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N62" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.05</v>
+        <v>3.79</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>3.5</v>
+        <v>1.84</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="M64" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.54</v>
+        <v>3.25</v>
       </c>
       <c r="M65" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8921,17 +8921,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.79</v>
+        <v>2.02</v>
       </c>
       <c r="M67" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N67" t="n">
-        <v>1.84</v>
+        <v>3.7</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9096,7 +9096,7 @@
         <v>2.2</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9308,17 +9308,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="M76" t="n">
-        <v>4</v>
+        <v>3.07</v>
       </c>
       <c r="N76" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="M84" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="N84" t="n">
-        <v>4.2</v>
+        <v>2.61</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M88" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N88" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12840,10 +12840,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="M97" t="n">
-        <v>3.76</v>
+        <v>3.45</v>
       </c>
       <c r="N97" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14130,10 +14130,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="M107" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="N107" t="n">
-        <v>3.73</v>
+        <v>2.9</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="Z107" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="M109" t="n">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="N109" t="n">
-        <v>3.25</v>
+        <v>3.73</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.52</v>
+        <v>2.55</v>
       </c>
       <c r="M112" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N112" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>8.5</v>
+        <v>1.72</v>
       </c>
       <c r="M114" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="N114" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,16 +15156,16 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="M116" t="n">
         <v>3.85</v>
       </c>
       <c r="N116" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,49 +15762,49 @@
         </is>
       </c>
       <c r="L119" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M119" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N119" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="n">
         <v>1.8</v>
       </c>
-      <c r="M119" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N119" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" t="n">
-        <v>0</v>
-      </c>
-      <c r="W119" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y119" t="n">
-        <v>1.7</v>
-      </c>
       <c r="Z119" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK135"/>
+  <dimension ref="A1:AK139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45933.44791666666</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45933.46875</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45933.47916666666</v>
+        <v>45933.46875</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
         <v>2.17</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.47916666666</v>
       </c>
     </row>
     <row r="32">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45933.52083333334</v>
+        <v>45933.5</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45933.54166666666</v>
+        <v>45933.52083333334</v>
       </c>
     </row>
     <row r="37">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.29</v>
+        <v>2.08</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>3.56</v>
       </c>
       <c r="N37" t="n">
-        <v>7.2</v>
+        <v>2.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5487,10 +5487,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45933.5625</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45933.5625</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45933.57291666666</v>
+        <v>45933.5625</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="M48" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>1.84</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.5625</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.57291666666</v>
       </c>
     </row>
     <row r="50">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7539,10 +7539,10 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -8239,27 +8239,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M66" t="n">
         <v>3.2</v>
       </c>
-      <c r="M66" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N66" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
         <v>2.2</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="M67" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N67" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9308,17 +9308,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="M70" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="M72" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N72" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="M74" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N74" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="75">
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="M84" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="N84" t="n">
-        <v>2.61</v>
+        <v>2.21</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.75</v>
+        <v>2.69</v>
       </c>
       <c r="M87" t="n">
-        <v>3.23</v>
+        <v>3.58</v>
       </c>
       <c r="N87" t="n">
-        <v>4.2</v>
+        <v>2.39</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="M88" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.28</v>
+        <v>1.65</v>
       </c>
       <c r="M89" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="N89" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11937,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45933.63541666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45933.63541666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="96">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12840,10 +12840,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="97">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="M97" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="N97" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Z97" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.63541666666</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.63541666666</v>
       </c>
     </row>
     <row r="100">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13485,10 +13485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="106">
@@ -14044,27 +14044,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>8.5</v>
+        <v>1.67</v>
       </c>
       <c r="M106" t="n">
-        <v>5.4</v>
+        <v>3.74</v>
       </c>
       <c r="N106" t="n">
-        <v>1.3</v>
+        <v>3.93</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14130,10 +14130,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="107">
@@ -14173,27 +14173,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M107" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N107" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="108">
@@ -14302,27 +14302,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="109">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,49 +14601,49 @@
         </is>
       </c>
       <c r="L110" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M110" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="N110" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
         <v>1.8</v>
       </c>
-      <c r="M110" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N110" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" t="n">
-        <v>0</v>
-      </c>
-      <c r="U110" t="n">
-        <v>0</v>
-      </c>
-      <c r="V110" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" t="n">
-        <v>0</v>
-      </c>
-      <c r="X110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>1.7</v>
-      </c>
       <c r="Z110" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="M112" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N112" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.52</v>
+        <v>8.5</v>
       </c>
       <c r="M113" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="N113" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15033,10 +15033,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="M114" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N114" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="Z114" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="M116" t="n">
-        <v>3.85</v>
+        <v>3.23</v>
       </c>
       <c r="N116" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="M119" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N119" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15850,27 +15850,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16023,10 +16023,10 @@
         <v>2.05</v>
       </c>
       <c r="M121" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N121" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="123">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="124">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,14 +16536,14 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="M125" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N125" t="n">
         <v>3.5</v>
       </c>
-      <c r="N125" t="n">
-        <v>3.2</v>
-      </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45933.67708333334</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="126">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45933.67708333334</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="127">
@@ -16753,27 +16753,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="AK127" s="3" t="n">
-        <v>45933.75</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="128">
@@ -16882,27 +16882,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="129">
@@ -17011,27 +17011,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.67708333334</v>
       </c>
     </row>
     <row r="130">
@@ -17140,27 +17140,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.67708333334</v>
       </c>
     </row>
     <row r="131">
@@ -17269,27 +17269,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.75</v>
       </c>
     </row>
     <row r="132">
@@ -17398,12 +17398,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17518,7 +17518,7 @@
         <v>0</v>
       </c>
       <c r="AK132" s="3" t="n">
-        <v>45933.8125</v>
+        <v>45933.79166666666</v>
       </c>
     </row>
     <row r="133">
@@ -17527,12 +17527,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17647,7 +17647,7 @@
         <v>0</v>
       </c>
       <c r="AK133" s="3" t="n">
-        <v>45933.875</v>
+        <v>45933.79166666666</v>
       </c>
     </row>
     <row r="134">
@@ -17656,12 +17656,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="AK134" s="3" t="n">
-        <v>45933.89583333334</v>
+        <v>45933.79166666666</v>
       </c>
     </row>
     <row r="135">
@@ -17785,126 +17785,642 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK135" s="3" t="n">
+        <v>45933.79166666666</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M136" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N136" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" s="3" t="n">
+        <v>45933.8125</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Houston Dash</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Orlando Pride</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK137" s="3" t="n">
+        <v>45933.875</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK138" s="3" t="n">
+        <v>45933.89583333334</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="inlineStr">
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK135" s="3" t="n">
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK139" s="3" t="n">
         <v>45933.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.04</v>
+        <v>2.41</v>
       </c>
       <c r="M35" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N35" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.29</v>
+        <v>3.5</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="N39" t="n">
-        <v>7.2</v>
+        <v>1.85</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.03</v>
+        <v>4.2</v>
       </c>
       <c r="M47" t="n">
         <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>3.45</v>
+        <v>1.84</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4.2</v>
+        <v>2.03</v>
       </c>
       <c r="M48" t="n">
         <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6894,10 +6894,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7539,10 +7539,10 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="M67" t="n">
         <v>2.95</v>
       </c>
       <c r="N67" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="M68" t="n">
         <v>2.95</v>
       </c>
       <c r="N68" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="M69" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,10 +9570,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="M71" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
         <v>2.3</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M74" t="n">
         <v>3.2</v>
       </c>
-      <c r="M74" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N74" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9999,7 +9999,7 @@
         <v>2.2</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="M75" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="N75" t="n">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10389,10 +10389,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="M85" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N85" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="M87" t="n">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="N87" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Z87" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11937,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="M101" t="n">
-        <v>3.76</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,16 +13479,16 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="M106" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="N106" t="n">
-        <v>3.93</v>
+        <v>3.34</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14130,10 +14130,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14388,10 +14388,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="M111" t="n">
         <v>3.85</v>
       </c>
       <c r="N111" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.25</v>
+        <v>1.45</v>
       </c>
       <c r="M112" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="N112" t="n">
-        <v>2.1</v>
+        <v>6.9</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>8.5</v>
+        <v>3.25</v>
       </c>
       <c r="M113" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="N113" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,16 +15027,16 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA113" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="M114" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N114" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="M115" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="N115" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="M116" t="n">
-        <v>3.23</v>
+        <v>3.85</v>
       </c>
       <c r="N116" t="n">
-        <v>2.74</v>
+        <v>3.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.35</v>
+        <v>8.5</v>
       </c>
       <c r="M117" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="N117" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.45</v>
+        <v>2.45</v>
       </c>
       <c r="M123" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="N123" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="Z123" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16758,22 +16758,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.04</v>
+        <v>2.41</v>
       </c>
       <c r="M34" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.41</v>
+        <v>3.04</v>
       </c>
       <c r="M35" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N35" t="n">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5358,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="M39" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="N39" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N47" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.79</v>
       </c>
       <c r="N48" t="n">
-        <v>3.45</v>
+        <v>2.81</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="N49" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6894,10 +6894,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.54</v>
+        <v>3.79</v>
       </c>
       <c r="M65" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="M67" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M68" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.45</v>
+        <v>2.54</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N69" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,16 +9351,16 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N71" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M73" t="n">
         <v>3.25</v>
       </c>
-      <c r="M73" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N73" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.79</v>
+        <v>2.85</v>
       </c>
       <c r="M74" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N74" t="n">
-        <v>1.84</v>
+        <v>2.6</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.65</v>
+        <v>2.87</v>
       </c>
       <c r="M77" t="n">
-        <v>4.15</v>
+        <v>3.14</v>
       </c>
       <c r="N77" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.87</v>
+        <v>1.75</v>
       </c>
       <c r="M79" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="N79" t="n">
-        <v>2.21</v>
+        <v>4.2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="M80" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="N80" t="n">
-        <v>2.18</v>
+        <v>3.14</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12066,10 +12066,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12195,10 +12195,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.06</v>
+        <v>2.95</v>
       </c>
       <c r="M97" t="n">
-        <v>3.07</v>
+        <v>3.55</v>
       </c>
       <c r="N97" t="n">
-        <v>3.25</v>
+        <v>2.18</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N101" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z101" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14001,10 +14001,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14130,10 +14130,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="M108" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="N108" t="n">
-        <v>3.93</v>
+        <v>3.34</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,16 +14382,16 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.05</v>
+        <v>8.5</v>
       </c>
       <c r="M111" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="N111" t="n">
-        <v>3.25</v>
+        <v>1.3</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,16 +14769,16 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="M114" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N114" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="Z114" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="M116" t="n">
         <v>3.85</v>
       </c>
       <c r="N116" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15549,10 +15549,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M118" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N118" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.45</v>
+        <v>1.45</v>
       </c>
       <c r="M123" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="N123" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17994,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18213,13 +18213,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18252,10 +18252,10 @@
         <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z138" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA138" t="n">
         <v>0</v>

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.41</v>
+        <v>3.04</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N34" t="n">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.29</v>
+        <v>3.5</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="N38" t="n">
-        <v>7.2</v>
+        <v>1.85</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.08</v>
+        <v>7.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="N45" t="n">
-        <v>2.79</v>
+        <v>1.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z45" t="n">
         <v>1.9</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7926,10 +7926,10 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.02</v>
+        <v>3.79</v>
       </c>
       <c r="M62" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>3.7</v>
+        <v>1.84</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8451,7 +8451,7 @@
         <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.05</v>
+        <v>2.54</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N63" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,16 +8577,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB63" t="n">
         <v>1.64</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.79</v>
+        <v>3.18</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="N65" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="M67" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N67" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="M69" t="n">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="N69" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,16 +9351,16 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="M70" t="n">
         <v>3.1</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="M71" t="n">
         <v>2.95</v>
       </c>
       <c r="N71" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="M72" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N72" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="M74" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N74" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="M77" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="N77" t="n">
-        <v>2.21</v>
+        <v>2.61</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="M79" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M80" t="n">
-        <v>3.32</v>
+        <v>3.07</v>
       </c>
       <c r="N80" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M82" t="n">
-        <v>3.05</v>
+        <v>3.32</v>
       </c>
       <c r="N82" t="n">
-        <v>2.61</v>
+        <v>3.14</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12066,10 +12066,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12195,10 +12195,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.06</v>
+        <v>2.69</v>
       </c>
       <c r="M92" t="n">
-        <v>3.07</v>
+        <v>3.58</v>
       </c>
       <c r="N92" t="n">
-        <v>3.25</v>
+        <v>2.39</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="M95" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="N95" t="n">
-        <v>2.39</v>
+        <v>2.07</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,16 +12705,16 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="M100" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N100" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z100" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="M101" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14001,10 +14001,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,16 +14253,16 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="M108" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="N108" t="n">
-        <v>3.34</v>
+        <v>3.93</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,16 +14382,16 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="M109" t="n">
-        <v>3.67</v>
+        <v>3.85</v>
       </c>
       <c r="N109" t="n">
-        <v>3.73</v>
+        <v>3.25</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="Z109" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="M113" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N113" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="M118" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N118" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="Z118" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.52</v>
+        <v>1.89</v>
       </c>
       <c r="M120" t="n">
-        <v>3.23</v>
+        <v>3.67</v>
       </c>
       <c r="N120" t="n">
-        <v>2.74</v>
+        <v>3.73</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="M121" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N121" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.35</v>
+        <v>2.52</v>
       </c>
       <c r="M122" t="n">
-        <v>4.9</v>
+        <v>3.23</v>
       </c>
       <c r="N122" t="n">
-        <v>7.2</v>
+        <v>2.74</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z122" t="n">
         <v>1.67</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>2.08</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.45</v>
+        <v>2.45</v>
       </c>
       <c r="M123" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="N123" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="Z123" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.41</v>
+        <v>3.04</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N32" t="n">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="M41" t="n">
-        <v>3.21</v>
+        <v>3.56</v>
       </c>
       <c r="N41" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.29</v>
+        <v>2.16</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>3.21</v>
       </c>
       <c r="N44" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7926,10 +7926,10 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.79</v>
+        <v>2.05</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>1.84</v>
+        <v>3.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.54</v>
+        <v>3.18</v>
       </c>
       <c r="M63" t="n">
         <v>3.41</v>
       </c>
       <c r="N63" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,16 +8577,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="M65" t="n">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="N65" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="M66" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="N66" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,16 +8964,16 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
       <c r="M67" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="M70" t="n">
         <v>3.1</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.85</v>
+        <v>3.79</v>
       </c>
       <c r="M71" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>2.6</v>
+        <v>1.84</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="M72" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N72" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="M77" t="n">
-        <v>3.05</v>
+        <v>4.15</v>
       </c>
       <c r="N77" t="n">
-        <v>2.61</v>
+        <v>4.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z77" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>0</v>
-      </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.28</v>
+        <v>2.87</v>
       </c>
       <c r="M79" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="N79" t="n">
-        <v>3.05</v>
+        <v>2.21</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="M80" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="N80" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="M81" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="N81" t="n">
-        <v>4.2</v>
+        <v>2.61</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="M86" t="n">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="N86" t="n">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11937,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="M100" t="n">
-        <v>3.31</v>
+        <v>3.76</v>
       </c>
       <c r="N100" t="n">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,16 +13350,16 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.97</v>
+        <v>4.7</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N101" t="n">
-        <v>3.1</v>
+        <v>1.63</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14130,10 +14130,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.98</v>
+        <v>2.9</v>
       </c>
       <c r="M107" t="n">
-        <v>3.76</v>
+        <v>3.1</v>
       </c>
       <c r="N107" t="n">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,16 +14253,16 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="M108" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="N108" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,16 +14382,16 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="M109" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N109" t="n">
-        <v>3.25</v>
+        <v>1.74</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14646,10 +14646,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>8.5</v>
+        <v>3.25</v>
       </c>
       <c r="M111" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="N111" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,16 +14769,16 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.8</v>
+        <v>2.52</v>
       </c>
       <c r="M113" t="n">
-        <v>3.85</v>
+        <v>3.23</v>
       </c>
       <c r="N113" t="n">
-        <v>3.7</v>
+        <v>2.74</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="M115" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="N115" t="n">
-        <v>6.9</v>
+        <v>4.2</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.35</v>
+        <v>1.89</v>
       </c>
       <c r="M117" t="n">
-        <v>4.9</v>
+        <v>3.67</v>
       </c>
       <c r="N117" t="n">
-        <v>7.2</v>
+        <v>3.73</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M118" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N118" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="M120" t="n">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="N120" t="n">
-        <v>3.73</v>
+        <v>2.6</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z120" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.52</v>
+        <v>1.45</v>
       </c>
       <c r="M122" t="n">
-        <v>3.23</v>
+        <v>4.7</v>
       </c>
       <c r="N122" t="n">
-        <v>2.74</v>
+        <v>6.9</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16242,22 +16242,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="M123" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N123" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK139"/>
+  <dimension ref="A1:AK137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45933.41666666666</v>
+        <v>45933.4375</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45933.4375</v>
+        <v>45933.44791666666</v>
       </c>
     </row>
     <row r="17">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45933.44791666666</v>
+        <v>45933.45833333334</v>
       </c>
     </row>
     <row r="19">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45933.45833333334</v>
+        <v>45933.46875</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45933.45833333334</v>
+        <v>45933.47916666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>2.53</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45933.45833333334</v>
+        <v>45933.5</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45933.46875</v>
+        <v>45933.5</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.61</v>
+        <v>3.04</v>
       </c>
       <c r="M31" t="n">
-        <v>3.14</v>
+        <v>3.56</v>
       </c>
       <c r="N31" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45933.47916666666</v>
+        <v>45933.5</v>
       </c>
     </row>
     <row r="32">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.52083333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45933.5</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="36">
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45933.52083333334</v>
+        <v>45933.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="M38" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="N38" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="M44" t="n">
-        <v>3.21</v>
+        <v>3.56</v>
       </c>
       <c r="N44" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N45" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45933.54166666666</v>
+        <v>45933.5625</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45933.54166666666</v>
+        <v>45933.5625</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.8</v>
+        <v>2.23</v>
       </c>
       <c r="M47" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="N47" t="n">
-        <v>1.85</v>
+        <v>2.98</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45933.5625</v>
+        <v>45933.57291666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="M48" t="n">
-        <v>3.79</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45933.5625</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45933.57291666666</v>
+        <v>45933.58333333334</v>
       </c>
     </row>
     <row r="50">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="M50" t="n">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="N50" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="N56" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7668,16 +7668,16 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="M61" t="n">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,16 +8313,16 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45933.58333333334</v>
+        <v>45933.60416666666</v>
       </c>
     </row>
     <row r="62">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.18</v>
+        <v>2.05</v>
       </c>
       <c r="M63" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="M64" t="n">
         <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.54</v>
+        <v>3.45</v>
       </c>
       <c r="M66" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,16 +8964,16 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="M67" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="N67" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.02</v>
+        <v>3.79</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N68" t="n">
-        <v>3.7</v>
+        <v>1.84</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9225,7 +9225,7 @@
         <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="M69" t="n">
         <v>2.95</v>
       </c>
       <c r="N69" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.79</v>
+        <v>1.49</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="N71" t="n">
-        <v>1.84</v>
+        <v>5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.45</v>
+        <v>2.54</v>
       </c>
       <c r="M72" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N72" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,16 +9738,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="74">
@@ -9916,27 +9916,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45933.60416666666</v>
+        <v>45933.625</v>
       </c>
     </row>
     <row r="75">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="M75" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="N75" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M76" t="n">
-        <v>3.32</v>
+        <v>3.07</v>
       </c>
       <c r="N76" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>4.15</v>
+        <v>3.32</v>
       </c>
       <c r="N77" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.28</v>
+        <v>2.95</v>
       </c>
       <c r="M80" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N80" t="n">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.95</v>
+        <v>1.65</v>
       </c>
       <c r="M89" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="N89" t="n">
-        <v>2.07</v>
+        <v>4.4</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11937,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.63541666666</v>
       </c>
     </row>
     <row r="97">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="M97" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N97" t="n">
-        <v>2.18</v>
+        <v>2.91</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45933.625</v>
+        <v>45933.63541666666</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45933.63541666666</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="M99" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="N99" t="n">
-        <v>2.91</v>
+        <v>3.93</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,16 +13221,16 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45933.63541666666</v>
+        <v>45933.64583333334</v>
       </c>
     </row>
     <row r="100">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,16 +13350,16 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="M103" t="n">
-        <v>3.31</v>
+        <v>3.76</v>
       </c>
       <c r="N103" t="n">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,16 +13737,16 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13989,16 +13989,16 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="M106" t="n">
-        <v>3.74</v>
+        <v>3.31</v>
       </c>
       <c r="N106" t="n">
-        <v>3.93</v>
+        <v>2.59</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14173,27 +14173,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="108">
@@ -14302,12 +14302,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
       <c r="M108" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="N108" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z108" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45933.64583333334</v>
+        <v>45933.65625</v>
       </c>
     </row>
     <row r="109">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.9</v>
+        <v>1.78</v>
       </c>
       <c r="M109" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="N109" t="n">
-        <v>1.74</v>
+        <v>3.51</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14646,10 +14646,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>3.25</v>
+        <v>1.35</v>
       </c>
       <c r="M111" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="N111" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.52</v>
+        <v>2.07</v>
       </c>
       <c r="M113" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="N113" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.35</v>
+        <v>2.6</v>
       </c>
       <c r="M114" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="N114" t="n">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="Z114" t="n">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.72</v>
+        <v>2.13</v>
       </c>
       <c r="M115" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="N115" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.89</v>
+        <v>8</v>
       </c>
       <c r="M117" t="n">
-        <v>3.67</v>
+        <v>5.3</v>
       </c>
       <c r="N117" t="n">
-        <v>3.73</v>
+        <v>1.24</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="M118" t="n">
-        <v>3.85</v>
+        <v>3.47</v>
       </c>
       <c r="N118" t="n">
-        <v>3.7</v>
+        <v>2.04</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="Z118" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="M119" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N119" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="M120" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="N120" t="n">
-        <v>2.6</v>
+        <v>3.73</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16108,27 +16108,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="123">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.05</v>
+        <v>2.61</v>
       </c>
       <c r="M123" t="n">
-        <v>3.85</v>
+        <v>3.31</v>
       </c>
       <c r="N123" t="n">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="Z123" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45933.65625</v>
+        <v>45933.66666666666</v>
       </c>
     </row>
     <row r="124">
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16753,12 +16753,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="AK127" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.67708333334</v>
       </c>
     </row>
     <row r="128">
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45933.66666666666</v>
+        <v>45933.67708333334</v>
       </c>
     </row>
     <row r="129">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45933.67708333334</v>
+        <v>45933.75</v>
       </c>
     </row>
     <row r="130">
@@ -17140,27 +17140,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45933.67708333334</v>
+        <v>45933.79166666666</v>
       </c>
     </row>
     <row r="131">
@@ -17269,27 +17269,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45933.75</v>
+        <v>45933.79166666666</v>
       </c>
     </row>
     <row r="132">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17656,12 +17656,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="AK134" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.8125</v>
       </c>
     </row>
     <row r="135">
@@ -17785,12 +17785,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="M135" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N135" t="n">
-        <v>4.8</v>
+        <v>1.65</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="Z135" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>
@@ -17905,7 +17905,7 @@
         <v>0</v>
       </c>
       <c r="AK135" s="3" t="n">
-        <v>45933.79166666666</v>
+        <v>45933.875</v>
       </c>
     </row>
     <row r="136">
@@ -17914,12 +17914,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.28</v>
+        <v>1.46</v>
       </c>
       <c r="M136" t="n">
-        <v>2.99</v>
+        <v>3.57</v>
       </c>
       <c r="N136" t="n">
-        <v>2.89</v>
+        <v>6.5</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -17994,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z136" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18034,7 +18034,7 @@
         <v>0</v>
       </c>
       <c r="AK136" s="3" t="n">
-        <v>45933.8125</v>
+        <v>45933.89583333334</v>
       </c>
     </row>
     <row r="137">
@@ -18043,12 +18043,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18117,16 +18117,16 @@
         <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X137" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y137" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z137" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA137" t="n">
         <v>0</v>
@@ -18163,264 +18163,6 @@
         <v>0</v>
       </c>
       <c r="AK137" s="3" t="n">
-        <v>45933.875</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>45933</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M138" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N138" t="n">
-        <v>7</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK138" s="3" t="n">
-        <v>45933.89583333334</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>45933</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK139" s="3" t="n">
         <v>45933.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.53</v>
+        <v>6.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.41</v>
+        <v>2.34</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="N30" t="n">
-        <v>6.4</v>
+        <v>2.53</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="M38" t="n">
-        <v>3.21</v>
+        <v>3.41</v>
       </c>
       <c r="N38" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.94</v>
+        <v>7.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>3.21</v>
+        <v>1.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.08</v>
+        <v>1.29</v>
       </c>
       <c r="M44" t="n">
-        <v>3.56</v>
+        <v>6</v>
       </c>
       <c r="N44" t="n">
-        <v>2.79</v>
+        <v>7.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7668,10 +7668,10 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7797,10 +7797,10 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="M61" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N61" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="M62" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="N62" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M64" t="n">
         <v>3.2</v>
       </c>
-      <c r="M64" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N64" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8709,7 +8709,7 @@
         <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8841,10 +8841,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.45</v>
+        <v>1.49</v>
       </c>
       <c r="M66" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N66" t="n">
-        <v>2.07</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.18</v>
+        <v>2.05</v>
       </c>
       <c r="M67" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.79</v>
+        <v>2.02</v>
       </c>
       <c r="M68" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>1.84</v>
+        <v>3.7</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9225,7 +9225,7 @@
         <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="M69" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9437,17 +9437,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.49</v>
+        <v>3.25</v>
       </c>
       <c r="M71" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="M72" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N72" t="n">
         <v>2.3</v>
@@ -9738,16 +9738,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="M77" t="n">
-        <v>3.32</v>
+        <v>3.14</v>
       </c>
       <c r="N77" t="n">
-        <v>3.14</v>
+        <v>2.21</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="M78" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N78" t="n">
-        <v>4.2</v>
+        <v>2.18</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10647,10 +10647,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="M80" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N80" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11937,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="M91" t="n">
-        <v>3.58</v>
+        <v>3.39</v>
       </c>
       <c r="N91" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M96" t="n">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="N96" t="n">
-        <v>6.4</v>
+        <v>2.91</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12837,7 +12837,7 @@
         <v>1.65</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="M97" t="n">
-        <v>3.34</v>
+        <v>5</v>
       </c>
       <c r="N97" t="n">
-        <v>2.91</v>
+        <v>6.4</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12966,7 +12966,7 @@
         <v>1.65</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.67</v>
+        <v>4.7</v>
       </c>
       <c r="M99" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="N99" t="n">
-        <v>3.93</v>
+        <v>1.63</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13227,10 +13227,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.7</v>
+        <v>1.97</v>
       </c>
       <c r="M101" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>1.63</v>
+        <v>3.1</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="M106" t="n">
-        <v>3.31</v>
+        <v>3.74</v>
       </c>
       <c r="N106" t="n">
-        <v>2.59</v>
+        <v>3.93</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="M108" t="n">
-        <v>3.23</v>
+        <v>3.47</v>
       </c>
       <c r="N108" t="n">
-        <v>2.74</v>
+        <v>2.04</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.35</v>
+        <v>3.9</v>
       </c>
       <c r="M111" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="N111" t="n">
-        <v>7.2</v>
+        <v>1.74</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.41</v>
+        <v>1.89</v>
       </c>
       <c r="M112" t="n">
-        <v>4.1</v>
+        <v>3.67</v>
       </c>
       <c r="N112" t="n">
-        <v>6</v>
+        <v>3.73</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14901,7 +14901,7 @@
         <v>1.8</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.07</v>
+        <v>1.41</v>
       </c>
       <c r="M113" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="N113" t="n">
-        <v>2.96</v>
+        <v>6</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.6</v>
+        <v>8</v>
       </c>
       <c r="M114" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="N114" t="n">
-        <v>2.6</v>
+        <v>1.24</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,16 +15156,16 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.67</v>
+        <v>2.41</v>
       </c>
       <c r="M116" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N116" t="n">
-        <v>3.99</v>
+        <v>2.58</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>8</v>
+        <v>2.13</v>
       </c>
       <c r="M117" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N117" t="n">
-        <v>1.24</v>
+        <v>3.1</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15549,10 +15549,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="M118" t="n">
-        <v>3.47</v>
+        <v>3.23</v>
       </c>
       <c r="N118" t="n">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="M119" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N119" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="M120" t="n">
-        <v>3.67</v>
+        <v>4.9</v>
       </c>
       <c r="N120" t="n">
-        <v>3.73</v>
+        <v>7.2</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z120" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
       <c r="M121" t="n">
         <v>3.7</v>
       </c>
       <c r="N121" t="n">
-        <v>1.74</v>
+        <v>3.99</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G133" t="n">

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.08</v>
+        <v>7.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2.79</v>
+        <v>1.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z34" t="n">
         <v>1.9</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="M38" t="n">
         <v>3.41</v>
       </c>
       <c r="N38" t="n">
-        <v>1.85</v>
+        <v>3.21</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>7.5</v>
+        <v>1.29</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="M41" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="N41" t="n">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.29</v>
+        <v>3.5</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="N44" t="n">
-        <v>7.2</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7668,10 +7668,10 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7797,10 +7797,10 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="M60" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N60" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.85</v>
+        <v>3.79</v>
       </c>
       <c r="M61" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>2.6</v>
+        <v>1.84</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="M62" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="M63" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N63" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.79</v>
+        <v>2.05</v>
       </c>
       <c r="M64" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>1.84</v>
+        <v>3.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.54</v>
+        <v>3.18</v>
       </c>
       <c r="M65" t="n">
         <v>3.41</v>
       </c>
       <c r="N65" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,16 +8835,16 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.49</v>
+        <v>2.54</v>
       </c>
       <c r="M66" t="n">
-        <v>4.4</v>
+        <v>3.41</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8970,10 +8970,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.02</v>
+        <v>3.45</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>3.7</v>
+        <v>2.07</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N69" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.25</v>
+        <v>1.49</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="N71" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.65</v>
+        <v>2.95</v>
       </c>
       <c r="M79" t="n">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="N79" t="n">
-        <v>4.4</v>
+        <v>2.18</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N80" t="n">
-        <v>3.15</v>
+        <v>2.61</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11163,10 +11163,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11550,10 +11550,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="N91" t="n">
-        <v>1.93</v>
+        <v>3.14</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="M96" t="n">
-        <v>3.34</v>
+        <v>5</v>
       </c>
       <c r="N96" t="n">
-        <v>2.91</v>
+        <v>6.4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12837,7 +12837,7 @@
         <v>1.65</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M97" t="n">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="N97" t="n">
-        <v>6.4</v>
+        <v>2.91</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12966,7 +12966,7 @@
         <v>1.65</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="M98" t="n">
-        <v>3.31</v>
+        <v>3.76</v>
       </c>
       <c r="N98" t="n">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13356,10 +13356,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,16 +13737,16 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.68</v>
+        <v>2.31</v>
       </c>
       <c r="M105" t="n">
-        <v>3.11</v>
+        <v>3.31</v>
       </c>
       <c r="N105" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13989,16 +13989,16 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.67</v>
+        <v>2.68</v>
       </c>
       <c r="M106" t="n">
-        <v>3.74</v>
+        <v>3.11</v>
       </c>
       <c r="N106" t="n">
-        <v>3.93</v>
+        <v>2.66</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,22 +14118,22 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="M107" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N107" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="Z107" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.92</v>
+        <v>1.78</v>
       </c>
       <c r="M108" t="n">
-        <v>3.47</v>
+        <v>3.67</v>
       </c>
       <c r="N108" t="n">
-        <v>2.04</v>
+        <v>3.51</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
       <c r="M111" t="n">
         <v>3.7</v>
       </c>
       <c r="N111" t="n">
-        <v>1.74</v>
+        <v>3.99</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.89</v>
+        <v>2.41</v>
       </c>
       <c r="M112" t="n">
-        <v>3.67</v>
+        <v>3.15</v>
       </c>
       <c r="N112" t="n">
-        <v>3.73</v>
+        <v>2.58</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="Z112" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>8</v>
+        <v>2.07</v>
       </c>
       <c r="M114" t="n">
-        <v>5.3</v>
+        <v>3.34</v>
       </c>
       <c r="N114" t="n">
-        <v>1.24</v>
+        <v>2.96</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,16 +15156,16 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="M116" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N116" t="n">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.13</v>
+        <v>1.35</v>
       </c>
       <c r="M117" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="N117" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.52</v>
+        <v>1.41</v>
       </c>
       <c r="M118" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="N118" t="n">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="M119" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="N119" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.35</v>
+        <v>3.9</v>
       </c>
       <c r="M120" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="N120" t="n">
-        <v>7.2</v>
+        <v>1.74</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.67</v>
+        <v>8</v>
       </c>
       <c r="M121" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="N121" t="n">
-        <v>3.99</v>
+        <v>1.24</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,16 +16059,16 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M137" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="N137" t="n">
-        <v>4.05</v>
+        <v>3.79</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="M30" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.53</v>
+        <v>6.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="M31" t="n">
-        <v>3.56</v>
+        <v>3.36</v>
       </c>
       <c r="N31" t="n">
-        <v>2.17</v>
+        <v>2.53</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.41</v>
+        <v>3.04</v>
       </c>
       <c r="M32" t="n">
-        <v>4.1</v>
+        <v>3.56</v>
       </c>
       <c r="N32" t="n">
-        <v>6.4</v>
+        <v>2.17</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="M38" t="n">
-        <v>3.41</v>
+        <v>3.56</v>
       </c>
       <c r="N38" t="n">
-        <v>3.21</v>
+        <v>2.79</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5487,10 +5487,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="M40" t="n">
-        <v>3.56</v>
+        <v>3.21</v>
       </c>
       <c r="N40" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.16</v>
+        <v>7.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.21</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7152,10 +7152,10 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.67</v>
+        <v>1.89</v>
       </c>
       <c r="M56" t="n">
-        <v>2.51</v>
+        <v>3.57</v>
       </c>
       <c r="N56" t="n">
-        <v>2.89</v>
+        <v>3.23</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7668,16 +7668,16 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.25</v>
+        <v>2.54</v>
       </c>
       <c r="M62" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="N62" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,16 +8448,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="M63" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="M65" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="M66" t="n">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="N66" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,16 +8964,16 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9050,17 +9050,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N68" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="M69" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9437,17 +9437,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.49</v>
+        <v>3.2</v>
       </c>
       <c r="M71" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="M72" t="n">
         <v>3.1</v>
       </c>
       <c r="N72" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10389,10 +10389,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11163,10 +11163,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="M84" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="N84" t="n">
-        <v>4.2</v>
+        <v>2.61</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11550,10 +11550,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.87</v>
+        <v>1.65</v>
       </c>
       <c r="M88" t="n">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="N88" t="n">
-        <v>2.21</v>
+        <v>4.4</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,16 +11802,16 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="M94" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="N94" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M96" t="n">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="N96" t="n">
-        <v>6.4</v>
+        <v>2.91</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12837,7 +12837,7 @@
         <v>1.65</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="M97" t="n">
-        <v>3.34</v>
+        <v>5</v>
       </c>
       <c r="N97" t="n">
-        <v>2.91</v>
+        <v>6.4</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12966,7 +12966,7 @@
         <v>1.65</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,16 +13221,16 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>4.7</v>
+        <v>2.31</v>
       </c>
       <c r="M104" t="n">
-        <v>3.65</v>
+        <v>3.31</v>
       </c>
       <c r="N104" t="n">
-        <v>1.63</v>
+        <v>2.59</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="M105" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.78</v>
+        <v>2.52</v>
       </c>
       <c r="M108" t="n">
-        <v>3.67</v>
+        <v>3.23</v>
       </c>
       <c r="N108" t="n">
-        <v>3.51</v>
+        <v>2.74</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.07</v>
+        <v>3.9</v>
       </c>
       <c r="M114" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="N114" t="n">
-        <v>2.96</v>
+        <v>1.74</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.52</v>
+        <v>1.41</v>
       </c>
       <c r="M115" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="N115" t="n">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.13</v>
+        <v>1.35</v>
       </c>
       <c r="M116" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="N116" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.35</v>
+        <v>8</v>
       </c>
       <c r="M117" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="N117" t="n">
-        <v>7.2</v>
+        <v>1.24</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.41</v>
+        <v>2.92</v>
       </c>
       <c r="M118" t="n">
-        <v>4.1</v>
+        <v>3.47</v>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>2.04</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.92</v>
+        <v>1.78</v>
       </c>
       <c r="M119" t="n">
-        <v>3.47</v>
+        <v>3.67</v>
       </c>
       <c r="N119" t="n">
-        <v>2.04</v>
+        <v>3.51</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.9</v>
+        <v>1.89</v>
       </c>
       <c r="M120" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="N120" t="n">
-        <v>1.74</v>
+        <v>3.73</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>8</v>
+        <v>2.13</v>
       </c>
       <c r="M121" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N121" t="n">
-        <v>1.24</v>
+        <v>3.1</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16065,10 +16065,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G133" t="n">

--- a/jogos_2025-10-03.xlsx
+++ b/jogos_2025-10-03.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>7.23</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="M31" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.53</v>
+        <v>6.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4443,28 +4443,28 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="M37" t="n">
         <v>3.41</v>
       </c>
       <c r="N37" t="n">
-        <v>3.21</v>
+        <v>1.85</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.08</v>
+        <v>1.29</v>
       </c>
       <c r="M38" t="n">
-        <v>3.56</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.79</v>
+        <v>7.2</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>7.43</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.9</v>
+        <v>3.02</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.16</v>
+        <v>7.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.21</v>
+        <v>3.9</v>
       </c>
       <c r="N40" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>7.5</v>
+        <v>2.08</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>3.56</v>
       </c>
       <c r="N41" t="n">
-        <v>1.5</v>
+        <v>2.79</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
         <v>1.9</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="M44" t="n">
         <v>3.41</v>
       </c>
       <c r="N44" t="n">
-        <v>1.85</v>
+        <v>3.21</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.8</v>
+        <v>2.22</v>
       </c>
       <c r="M45" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="N45" t="n">
-        <v>1.85</v>
+        <v>2.81</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y45" t="n">
         <v>1.65</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="N46" t="n">
-        <v>2.81</v>
+        <v>1.85</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y46" t="n">
         <v>1.65</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6483,34 +6483,34 @@
         <v>2.98</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y47" t="n">
         <v>2.3</v>
@@ -6519,16 +6519,16 @@
         <v>1.6</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6870,13 +6870,13 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -6885,37 +6885,37 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.67</v>
+        <v>1.89</v>
       </c>
       <c r="M52" t="n">
-        <v>2.51</v>
+        <v>3.57</v>
       </c>
       <c r="N52" t="n">
-        <v>2.89</v>
+        <v>3.23</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.76</v>
+        <v>1.16</v>
       </c>
       <c r="X52" t="n">
-        <v>1.94</v>
+        <v>4.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7281,10 +7281,10 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.89</v>
+        <v>2.54</v>
       </c>
       <c r="M56" t="n">
-        <v>3.57</v>
+        <v>3.35</v>
       </c>
       <c r="N56" t="n">
-        <v>3.23</v>
+        <v>2.51</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,22 +8151,22 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
       <c r="M60" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="N60" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -8175,37 +8175,37 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.79</v>
+        <v>2.02</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N61" t="n">
-        <v>1.84</v>
+        <v>3.7</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y61" t="n">
         <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8418,40 +8418,40 @@
         <v>2.3</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA62" t="n">
         <v>2.13</v>
@@ -8460,10 +8460,10 @@
         <v>1.64</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,43 +8796,43 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="M65" t="n">
         <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y65" t="n">
         <v>2.2</v>
@@ -8841,16 +8841,16 @@
         <v>1.6</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.05</v>
+        <v>3.79</v>
       </c>
       <c r="M66" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N66" t="n">
-        <v>2.45</v>
+        <v>1.84</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9050,65 +9050,65 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="M68" t="n">
         <v>2.95</v>
       </c>
       <c r="N68" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N69" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,61 +9441,61 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="M70" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,61 +9570,61 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9708,34 +9708,34 @@
         <v>2.25</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y72" t="n">
         <v>2.2</v>
@@ -9744,16 +9744,16 @@
         <v>1.6</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="M73" t="n">
-        <v>3.23</v>
+        <v>4.15</v>
       </c>
       <c r="N73" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,61 +9957,61 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,61 +10215,61 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="M77" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="N77" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,61 +10731,61 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M82" t="n">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="N82" t="n">
-        <v>3.14</v>
+        <v>2.61</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,61 +11118,61 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,61 +11247,61 @@
         </is>
       </c>
       <c r="L84" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M84" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N84" t="n">
         <v>2.45</v>
       </c>
-      <c r="M84" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N84" t="n">
-        <v>2.61</v>
-      </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.3</v>
+        <v>1.46</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.62</v>
+        <v>2.39</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,61 +11376,61 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,61 +11505,61 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -11572,10 +11572,10 @@
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,61 +11634,61 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,61 +11763,61 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M88" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="N88" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
@@ -11830,10 +11830,10 @@
         </is>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,61 +11892,61 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="M89" t="n">
-        <v>3.09</v>
+        <v>3.7</v>
       </c>
       <c r="N89" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
@@ -11959,10 +11959,10 @@
         </is>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,61 +12021,61 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
@@ -12088,10 +12088,10 @@
         </is>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,61 +12150,61 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,61 +12279,61 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
@@ -12346,10 +12346,10 @@
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="M93" t="n">
-        <v>3.58</v>
+        <v>3.23</v>
       </c>
       <c r="N93" t="n">
-        <v>2.39</v>
+        <v>4.2</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,61 +12537,61 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="M94" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="N94" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE94" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,61 +12666,61 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="M95" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="N95" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
@@ -12733,10 +12733,10 @@
         </is>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI95" t="n">
         <v>0</v>
@@ -12804,34 +12804,34 @@
         <v>2.91</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y96" t="n">
         <v>1.65</v>
@@ -12840,16 +12840,16 @@
         <v>2.1</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
@@ -12862,10 +12862,10 @@
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -12933,34 +12933,34 @@
         <v>6.4</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y97" t="n">
         <v>1.65</v>
@@ -12969,16 +12969,16 @@
         <v>2.25</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13191,34 +13191,34 @@
         <v>3.34</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Y99" t="n">
         <v>1.57</v>
@@ -13233,10 +13233,10 @@
         <v>1.6</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
@@ -13320,40 +13320,40 @@
         <v>3.93</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA100" t="n">
         <v>2.17</v>
@@ -13362,10 +13362,10 @@
         <v>1.62</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
@@ -13378,10 +13378,10 @@
         </is>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,61 +13440,61 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE101" t="inlineStr">
         <is>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13731,16 +13731,16 @@
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.68</v>
+        <v>4.7</v>
       </c>
       <c r="M106" t="n">
-        <v>3.11</v>
+        <v>3.65</v>
       </c>
       <c r="N106" t="n">
-        <v>2.66</v>
+        <v>1.63</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,16 +14118,16 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="M107" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N107" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,61 +14343,61 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.52</v>
+        <v>8</v>
       </c>
       <c r="M108" t="n">
-        <v>3.23</v>
+        <v>5.3</v>
       </c>
       <c r="N108" t="n">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.67</v>
+        <v>2.42</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE108" t="inlineStr">
         <is>
@@ -14410,10 +14410,10 @@
         </is>
       </c>
       <c r="AG108" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,61 +14472,61 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="M109" t="n">
-        <v>3.34</v>
+        <v>3.67</v>
       </c>
       <c r="N109" t="n">
-        <v>2.96</v>
+        <v>3.51</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD109" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE109" t="inlineStr">
         <is>
@@ -14539,10 +14539,10 @@
         </is>
       </c>
       <c r="AG109" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,61 +14988,61 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.67</v>
+        <v>2.41</v>
       </c>
       <c r="M113" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N113" t="n">
-        <v>3.99</v>
+        <v>2.58</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH113" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,61 +15117,61 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
       <c r="M114" t="n">
         <v>3.7</v>
       </c>
       <c r="N114" t="n">
-        <v>1.74</v>
+        <v>3.99</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U114" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V114" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W114" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD114" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
@@ -15184,10 +15184,10 @@
         </is>
       </c>
       <c r="AG114" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH114" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>8</v>
+        <v>1.89</v>
       </c>
       <c r="M117" t="n">
-        <v>5.3</v>
+        <v>3.67</v>
       </c>
       <c r="N117" t="n">
-        <v>1.24</v>
+        <v>3.73</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="M118" t="n">
-        <v>3.47</v>
+        <v>3.23</v>
       </c>
       <c r="N118" t="n">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.78</v>
+        <v>3.9</v>
       </c>
       <c r="M119" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="N119" t="n">
-        <v>3.51</v>
+        <v>1.74</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,61 +15891,61 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.89</v>
+        <v>2.92</v>
       </c>
       <c r="M120" t="n">
-        <v>3.67</v>
+        <v>3.47</v>
       </c>
       <c r="N120" t="n">
-        <v>3.73</v>
+        <v>2.04</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X120" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z120" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE120" t="inlineStr">
         <is>
@@ -15958,10 +15958,10 @@
         </is>
       </c>
       <c r="AG120" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH120" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,61 +16020,61 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="M121" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N121" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W121" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
@@ -16087,10 +16087,10 @@
         </is>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -16242,22 +16242,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G133" t="n">
